--- a/Medical Devices.xlsx
+++ b/Medical Devices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C7E374-C5C4-498A-B1C8-7D34AFBEA31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7307E2-025D-4DED-9B40-1329335090B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40830" yWindow="2720" windowWidth="28980" windowHeight="14360" activeTab="1" xr2:uid="{74C39317-3ECA-46DC-8532-F0BC37DD93FC}"/>
+    <workbookView xWindow="11150" yWindow="4520" windowWidth="19050" windowHeight="16100" activeTab="3" xr2:uid="{74C39317-3ECA-46DC-8532-F0BC37DD93FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Resources" sheetId="4" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="224">
   <si>
     <t>Medtronic</t>
   </si>
@@ -169,9 +170,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>ACL SW</t>
-  </si>
-  <si>
     <t>Alcon</t>
   </si>
   <si>
@@ -460,9 +458,6 @@
     <t>CRL</t>
   </si>
   <si>
-    <t>Q222</t>
-  </si>
-  <si>
     <t>Sysmex</t>
   </si>
   <si>
@@ -715,9 +710,6 @@
     <t>Intuitive</t>
   </si>
   <si>
-    <t>Q424</t>
-  </si>
-  <si>
     <t>YourBio</t>
   </si>
   <si>
@@ -727,7 +719,13 @@
     <t>PHIA NA</t>
   </si>
   <si>
-    <t>Q115</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>ALC</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -918,22 +916,22 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>1747</v>
+          <cell r="H3">
+            <v>371</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>7751</v>
+          <cell r="H5">
+            <v>4064</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>13242</v>
+          <cell r="H6">
+            <v>42549</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -952,18 +950,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>132.020816</v>
+          <cell r="M3">
+            <v>283.90164199999998</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>892.84400000000005</v>
+          <cell r="M5">
+            <v>745</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>367.01799999999997</v>
+          <cell r="M6">
+            <v>16456</v>
           </cell>
         </row>
       </sheetData>
@@ -976,9 +974,6 @@
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
@@ -987,17 +982,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>51.630726000000003</v>
+            <v>621.75173600000005</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>411</v>
+            <v>3119.6000000000004</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>2409</v>
+            <v>595.9</v>
           </cell>
         </row>
       </sheetData>
@@ -1020,22 +1015,44 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>31.049147999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>958.84500000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>0</v>
+          <cell r="L3">
+            <v>27.943534</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>16.932341000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>4.3380000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1054,18 +1071,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>362</v>
+          <cell r="J3">
+            <v>702.98605399999997</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>8832</v>
+          <cell r="J5">
+            <v>4348</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>0</v>
+          <cell r="J6">
+            <v>26558</v>
           </cell>
         </row>
       </sheetData>
@@ -1078,6 +1095,9 @@
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
@@ -1086,17 +1106,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>378.15408000000002</v>
+            <v>132.020816</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>1530</v>
+            <v>892.84400000000005</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>14099</v>
+            <v>367.01799999999997</v>
           </cell>
         </row>
       </sheetData>
@@ -1114,23 +1134,23 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Models"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="M3">
-            <v>1330.423708</v>
+          <cell r="L3">
+            <v>51.630726000000003</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="M5">
-            <v>10573</v>
+          <cell r="L5">
+            <v>411</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="M6">
-            <v>24114</v>
+          <cell r="L6">
+            <v>2409</v>
           </cell>
         </row>
       </sheetData>
@@ -1153,18 +1173,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="M3">
-            <v>283.90164199999998</v>
+          <cell r="K3">
+            <v>31.049147999999999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="M5">
-            <v>745</v>
+          <cell r="K5">
+            <v>958.84500000000003</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="M6">
-            <v>16456</v>
+          <cell r="K6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -1177,6 +1197,9 @@
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
@@ -1185,21 +1208,21 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>621.75173600000005</v>
+            <v>1741.8124290000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>3119.6000000000004</v>
+            <v>8385</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>595.9</v>
+            <v>34047</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1218,50 +1241,28 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>27.943534</v>
+          <cell r="K3">
+            <v>354.16284200000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>7979.2000000000007</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="L3">
-            <v>16.932341000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="L5">
-            <v>4.3380000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1271,18 +1272,52 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="H3">
-            <v>391.78896200000003</v>
+          <cell r="L3">
+            <v>378.15408000000002</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>1888</v>
+          <cell r="L5">
+            <v>1530</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>30260</v>
+          <cell r="L6">
+            <v>14099</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Models"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="M3">
+            <v>1330.423708</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="M5">
+            <v>10573</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="M6">
+            <v>24114</v>
           </cell>
         </row>
       </sheetData>
@@ -1590,11 +1625,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9DDF09-9767-4626-AE33-17729200745B}">
   <dimension ref="B2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1607,19 +1642,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F79611-2BB3-4834-9AEA-2A0CCF755EDA}">
-  <dimension ref="A2:K66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:K65"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" style="2" customWidth="1"/>
-    <col min="4" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" style="2" customWidth="1"/>
+    <col min="4" max="9" width="9.1796875" style="1"/>
+    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
@@ -1631,27 +1666,27 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>22</v>
@@ -1660,76 +1695,76 @@
         <v>23</v>
       </c>
       <c r="D3" s="3">
-        <v>132.24</v>
+        <v>101</v>
       </c>
       <c r="E3" s="4">
         <f>+D3*H3</f>
-        <v>231023.28000000003</v>
+        <v>175923.055329</v>
       </c>
       <c r="F3" s="4">
-        <f>+[1]Main!$L$5-[1]Main!$L$6</f>
-        <v>-5491</v>
+        <f>+[6]Main!$L$5-[6]Main!$L$6</f>
+        <v>-25662</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G8" si="0">+E3-F3</f>
-        <v>236514.28000000003</v>
+        <v>201585.055329</v>
       </c>
       <c r="H3" s="4">
-        <f>+[1]Main!$L$3</f>
-        <v>1747</v>
+        <f>+[6]Main!$L$3</f>
+        <v>1741.8124290000001</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J3" s="16">
-        <v>45852</v>
+        <v>46220</v>
       </c>
       <c r="K3">
         <v>1900</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>590.70000000000005</v>
+        <v>365</v>
       </c>
       <c r="E4" s="4">
-        <f>+D4*[2]Main!$K$3</f>
-        <v>213833.40000000002</v>
+        <f>+D4*[7]Main!$K$3</f>
+        <v>129269.43733</v>
       </c>
       <c r="F4" s="4">
-        <f>+[2]Main!$K$5-[2]Main!$K$6</f>
-        <v>8832</v>
+        <f>+[7]Main!$K$5-[7]Main!$K$6</f>
+        <v>7979.2000000000007</v>
       </c>
       <c r="G4" s="4">
         <f>+E4-F4</f>
-        <v>205001.40000000002</v>
+        <v>121290.23733</v>
       </c>
       <c r="H4" s="4">
-        <f>+[2]Main!$K$3</f>
-        <v>362</v>
+        <f>+[7]Main!$K$3</f>
+        <v>354.16284200000001</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J4" s="16">
-        <v>45332</v>
+        <v>46220</v>
       </c>
       <c r="K4">
         <v>1995</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -1738,28 +1773,28 @@
         <v>8</v>
       </c>
       <c r="D5" s="3">
-        <v>358.98</v>
+        <v>322</v>
       </c>
       <c r="E5" s="4">
-        <f>+D5*[3]Main!$L$3</f>
-        <v>135749.75163840002</v>
+        <f>+D5*[8]Main!$L$3</f>
+        <v>121765.61376000001</v>
       </c>
       <c r="F5" s="4">
-        <f>+[3]Main!$L$5-[3]Main!$L$6</f>
+        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
         <v>-12569</v>
       </c>
       <c r="G5" s="4">
         <f>+E5-F5</f>
-        <v>148318.75163840002</v>
+        <v>134334.61376000001</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>0</v>
@@ -1768,31 +1803,31 @@
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <v>89.84</v>
+        <v>84</v>
       </c>
       <c r="E6" s="4">
-        <f>+D6*[4]Main!$M$3</f>
-        <v>119525.26592672001</v>
+        <f>+D6*[9]Main!$M$3</f>
+        <v>111755.591472</v>
       </c>
       <c r="F6" s="4">
-        <f>+[4]Main!$M$5-[4]Main!$M$6</f>
+        <f>+[9]Main!$M$5-[9]Main!$M$6</f>
         <v>-13541</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>133066.26592671999</v>
+        <v>125296.591472</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J6" s="16">
         <v>45014</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>28</v>
@@ -1801,26 +1836,26 @@
         <v>29</v>
       </c>
       <c r="D7" s="3">
-        <v>241.82</v>
+        <v>159</v>
       </c>
       <c r="E7" s="4">
         <f>+D7*H7</f>
-        <v>68653.095068439987</v>
+        <v>45140.361077999994</v>
       </c>
       <c r="F7" s="4">
-        <f>+[5]Main!$M$5-[5]Main!$M$6</f>
+        <f>+[10]Main!$M$5-[10]Main!$M$6</f>
         <v>-15711</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>84364.095068439987</v>
+        <v>60851.361077999994</v>
       </c>
       <c r="H7" s="4">
-        <f>+[5]Main!$M$3</f>
+        <f>+[10]Main!$M$3</f>
         <v>283.90164199999998</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J7" s="16">
         <v>44961</v>
@@ -1829,9 +1864,9 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>16</v>
@@ -1840,43 +1875,46 @@
         <v>17</v>
       </c>
       <c r="D8" s="3">
-        <v>68.900000000000006</v>
+        <v>86.64</v>
       </c>
       <c r="E8" s="4">
-        <f>+D8*[6]Main!$L$3</f>
-        <v>42838.694610400009</v>
+        <f>+D8*[11]Main!$L$3</f>
+        <v>53868.570407040002</v>
       </c>
       <c r="F8" s="4">
-        <f>+[6]Main!$L$5-[6]Main!$L$6</f>
+        <f>+[11]Main!$L$5-[11]Main!$L$6</f>
         <v>2523.7000000000003</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>40314.994610400012</v>
+        <v>51344.870407040005</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>30</v>
+      </c>
+      <c r="D9" s="3">
+        <v>167.15</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
@@ -1884,21 +1922,27 @@
       <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D10" s="3">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D11" s="1">
+        <v>35.130000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1906,392 +1950,446 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D12" s="1">
+        <v>150.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" s="1">
+        <v>70.290000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="1">
+        <v>132.41999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1">
+        <v>25215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="3">
+        <v>200.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="3">
+        <v>63.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3">
+        <v>186.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="1">
+        <v>176.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D20" s="1">
+        <v>566.91999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
-        <v>82</v>
+        <v>46</v>
+      </c>
+      <c r="D21" s="1">
+        <v>76.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="D22" s="3">
+        <v>195.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1311.23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>82</v>
+      <c r="D24" s="3">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="B25" t="s">
         <v>53</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+      <c r="D25" s="1">
+        <v>421.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="1">
+        <v>99.78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27" s="1">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
         <v>56</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="D28" s="1">
+        <v>365.22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1">
+        <v>92.19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" t="s">
-        <v>5</v>
-      </c>
       <c r="C30" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="2" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>203</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D35" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="2" t="s">
+    </row>
+    <row r="40" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="17" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>82</v>
-      </c>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>81</v>
+      </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
         <v>136</v>
@@ -2300,9 +2398,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
         <v>138</v>
@@ -2310,10 +2408,11 @@
       <c r="C49" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
         <v>140</v>
@@ -2323,9 +2422,9 @@
       </c>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
         <v>142</v>
@@ -2333,11 +2432,16 @@
       <c r="C51" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D51" s="1">
+        <v>134.15</v>
+      </c>
+      <c r="E51" s="4">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
         <v>144</v>
@@ -2346,178 +2450,161 @@
         <v>145</v>
       </c>
       <c r="D52" s="1">
-        <v>134.15</v>
+        <v>24.85</v>
       </c>
       <c r="E52" s="4">
-        <v>7100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>82</v>
-      </c>
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="3">
+        <v>79.349999999999994</v>
+      </c>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>205</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" s="3">
+        <v>43</v>
+      </c>
+      <c r="E54" s="4">
+        <f>+D54*H54</f>
+        <v>1201.571962</v>
+      </c>
+      <c r="G54" s="4">
+        <f>+E54-F54</f>
+        <v>1201.571962</v>
+      </c>
+      <c r="H54" s="4">
+        <f>[12]Main!$L$3</f>
+        <v>27.943534</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J54" s="16">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>146</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D53" s="1">
-        <v>24.85</v>
-      </c>
-      <c r="E53" s="4">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
-        <v>217</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D54" s="3">
-        <v>79.349999999999994</v>
-      </c>
-      <c r="E54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>207</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D55" s="3">
-        <v>43</v>
-      </c>
-      <c r="E55" s="4">
-        <f>+D55*H55</f>
-        <v>1201.571962</v>
-      </c>
-      <c r="G55" s="4">
-        <f>+E55-F55</f>
-        <v>1201.571962</v>
-      </c>
-      <c r="H55" s="4">
-        <f>[7]Main!$L$3</f>
-        <v>27.943534</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J55" s="16">
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="D56" s="1">
+        <v>13.59</v>
+      </c>
+      <c r="E56" s="4">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>81</v>
+      </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" s="1">
-        <v>13.59</v>
-      </c>
-      <c r="E57" s="4">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="E57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>82</v>
-      </c>
-      <c r="B60" t="s">
-        <v>179</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B61" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D61" s="3">
+        <v>213</v>
+      </c>
+      <c r="D60" s="3">
         <v>1.19</v>
       </c>
-      <c r="E61" s="4">
-        <f>+D61*H61</f>
+      <c r="E60" s="4">
+        <f>+D60*H60</f>
         <v>20.14948579</v>
       </c>
-      <c r="F61" s="4">
-        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
+      <c r="F60" s="4">
+        <f>+[13]Main!$L$5-[13]Main!$L$6</f>
         <v>4.3380000000000001</v>
       </c>
-      <c r="G61" s="4">
-        <f>+E61-F61</f>
+      <c r="G60" s="4">
+        <f>+E60-F60</f>
         <v>15.811485789999999</v>
       </c>
-      <c r="H61" s="4">
-        <f>+[8]Main!$L$3</f>
+      <c r="H60" s="4">
+        <f>+[13]Main!$L$3</f>
         <v>16.932341000000001</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J61" s="16">
+      <c r="I60" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J60" s="16">
         <v>45656</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>184</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>186</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G65" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2528,7 +2615,7 @@
     <hyperlink ref="B4" r:id="rId4" display="Intuitive Surgical" xr:uid="{D10C7206-D056-4649-84E3-48ED7255DCF8}"/>
     <hyperlink ref="B8" r:id="rId5" xr:uid="{8C8CFEF4-EC99-4BD1-8542-5F27AB3FBF8E}"/>
     <hyperlink ref="B7" r:id="rId6" xr:uid="{33504D51-2E3F-4370-BCBD-318C828A1903}"/>
-    <hyperlink ref="B61" r:id="rId7" xr:uid="{E6990DD6-A42D-4691-8BC6-541575837CB2}"/>
+    <hyperlink ref="B60" r:id="rId7" xr:uid="{E6990DD6-A42D-4691-8BC6-541575837CB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId8"/>
@@ -2538,23 +2625,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D23D8427-6593-41F3-A83F-2502A7FAEA38}">
   <dimension ref="A2:H5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2563,15 +2650,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2579,12 +2666,12 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2595,17 +2682,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85197DD-BC14-4968-9014-85046DB3F965}">
   <dimension ref="A2:X41"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="2"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" style="2"/>
+    <col min="10" max="10" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>2</v>
@@ -2617,49 +2704,49 @@
         <v>10</v>
       </c>
       <c r="F2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="P2" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="Q2" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="R2" s="15" t="s">
         <v>91</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>92</v>
       </c>
       <c r="S2" s="13">
         <v>2025</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U2" s="12">
         <v>2023</v>
@@ -2671,12 +2758,12 @@
         <v>2025</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>11</v>
@@ -2684,51 +2771,71 @@
       <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1">
-        <v>541.28</v>
+      <c r="D3" s="3">
+        <v>574</v>
       </c>
       <c r="E3" s="4">
         <f>+D3*H3</f>
-        <v>212067.52935135999</v>
+        <v>212954</v>
       </c>
       <c r="F3" s="4">
-        <f>+[9]Main!$H$5-[9]Main!$H$6</f>
-        <v>-28372</v>
+        <f>+[1]Main!$H$5-[1]Main!$H$6</f>
+        <v>-38485</v>
       </c>
       <c r="G3" s="4">
         <f>+E3-F3</f>
-        <v>240439.52935135999</v>
+        <v>251439</v>
       </c>
       <c r="H3" s="4">
-        <f>+[9]Main!$H$3</f>
-        <v>391.78896200000003</v>
+        <f>+[1]Main!$H$3</f>
+        <v>371</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="J3" s="16">
-        <v>44823</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="D4" s="3">
+        <v>170</v>
+      </c>
+      <c r="E4" s="4">
+        <f>+D4*H4</f>
+        <v>119507.62917999999</v>
+      </c>
+      <c r="F4" s="4">
+        <f>+[2]Main!$J$5-[2]Main!$J$6</f>
+        <v>-22210</v>
+      </c>
+      <c r="G4" s="4">
+        <f>+E4-F4</f>
+        <v>141717.62917999999</v>
+      </c>
+      <c r="H4" s="4">
+        <f>+[2]Main!$J$3</f>
+        <v>702.98605399999997</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J4" s="16">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -2742,9 +2849,9 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -2753,15 +2860,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2769,15 +2876,15 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2785,15 +2892,15 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2801,15 +2908,15 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -2818,15 +2925,15 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D11">
         <v>168.51</v>
@@ -2836,7 +2943,7 @@
         <v>22246.827704159998</v>
       </c>
       <c r="F11" s="21">
-        <f>+[10]Main!$L$5-[10]Main!$L$6</f>
+        <f>+[3]Main!$L$5-[3]Main!$L$6</f>
         <v>525.82600000000002</v>
       </c>
       <c r="G11" s="21">
@@ -2844,49 +2951,49 @@
         <v>21721.001704159997</v>
       </c>
       <c r="H11" s="21">
-        <f>+[10]Main!$L$3</f>
+        <f>+[3]Main!$L$3</f>
         <v>132.020816</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J11" s="16">
         <v>45632</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2900,73 +3007,73 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D21" s="20">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -2974,26 +3081,26 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="D24" s="20">
         <v>117</v>
@@ -3003,7 +3110,7 @@
         <v>6040.7949420000004</v>
       </c>
       <c r="F24" s="21">
-        <f>[11]Main!$L$5-[11]Main!$L$6</f>
+        <f>[4]Main!$L$5-[4]Main!$L$6</f>
         <v>-1998</v>
       </c>
       <c r="G24" s="21">
@@ -3011,54 +3118,54 @@
         <v>8038.7949420000004</v>
       </c>
       <c r="H24" s="21">
-        <f>+[11]Main!$L$3</f>
+        <f>+[4]Main!$L$3</f>
         <v>51.630726000000003</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J24" s="16">
         <v>45776</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D29">
         <v>14.06</v>
@@ -3068,7 +3175,7 @@
         <v>436.55102088000001</v>
       </c>
       <c r="F29" s="21">
-        <f>+[12]Main!$K$5-[12]Main!$K$6</f>
+        <f>+[5]Main!$K$5-[5]Main!$K$6</f>
         <v>958.84500000000003</v>
       </c>
       <c r="G29" s="21">
@@ -3076,108 +3183,108 @@
         <v>-522.29397912000002</v>
       </c>
       <c r="H29" s="21">
-        <f>+[12]Main!$K$3</f>
+        <f>+[5]Main!$K$3</f>
         <v>31.049147999999999</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J29" s="16">
         <v>45582</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D34">
         <v>2018</v>
       </c>
       <c r="E34" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" t="s">
         <v>183</v>
       </c>
-      <c r="F34" t="s">
-        <v>184</v>
-      </c>
-      <c r="G34" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" t="s">
         <v>190</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E35" t="s">
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>191</v>
       </c>
-      <c r="F35" t="s">
+      <c r="C36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>193</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E36" t="s">
-        <v>191</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="C37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+      <c r="F37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>195</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="C38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s">
         <v>196</v>
       </c>
-      <c r="F37" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>197</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E38" t="s">
-        <v>198</v>
-      </c>
       <c r="F38" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G41" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3186,6 +3293,7 @@
     <hyperlink ref="B29" r:id="rId2" xr:uid="{375547C2-8DD1-4612-A521-505020286C6F}"/>
     <hyperlink ref="B24" r:id="rId3" xr:uid="{3120593B-0D87-46D2-B21F-DE912F72E638}"/>
     <hyperlink ref="B11" r:id="rId4" xr:uid="{C0A4BE37-391D-46D8-9278-AF9FC4C01B3E}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{D6D006ED-3B15-40ED-8A04-E3EFF081AC1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3194,56 +3302,56 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDE9693-164E-4AE4-AD52-72E635F966BE}">
   <dimension ref="B2:D6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3">
         <v>2014</v>
       </c>
       <c r="D3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>168</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
